--- a/data/sars/keys/area_key_pacific_final.xlsx
+++ b/data/sars/keys/area_key_pacific_final.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10621"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cfree/Dropbox/Chris/UCSB/projects/marine_mammals/us_sar_synthesis/data/sars/keys/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1C88830-7611-9D4B-A74D-8A0557572CB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76D8D997-6FA6-6044-8A34-30F675531FBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="800" yWindow="4220" windowWidth="28040" windowHeight="17440" xr2:uid="{ECCE486D-1AB6-EC4A-BECA-C7CC166E6D83}"/>
   </bookViews>
@@ -3617,7 +3617,7 @@
         <v>6</v>
       </c>
       <c r="C163" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D163" t="s">
         <v>5</v>
